--- a/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CDA6D8B0-8AA7-4A0D-9362-6A697A2E9EA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{80C0C5E4-724C-4C89-9F9B-0BDD95E6D19B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{A8AA27E1-D97F-47F5-AD87-E53889905A34}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{8D7C1CD8-3749-4B8C-B92F-B5987F24910C}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -3763,7 +3763,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFD3A9F3-1698-4276-9968-89A5AB1BFD00}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD3E2C79-EBC6-48E7-9568-BE4609152FA8}">
   <dimension ref="B3:L489"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{80C0C5E4-724C-4C89-9F9B-0BDD95E6D19B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B23C6451-B33D-4994-BD91-5D8A9605BD9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{8D7C1CD8-3749-4B8C-B92F-B5987F24910C}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{51459B85-4443-4584-AD2F-9B49E04CBB96}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -3763,7 +3763,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD3E2C79-EBC6-48E7-9568-BE4609152FA8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03D80C54-9B97-43D1-A7DF-B0D00E836335}">
   <dimension ref="B3:L489"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B23C6451-B33D-4994-BD91-5D8A9605BD9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BA6B77CE-D63C-4B75-AE47-4F3D78462FF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{51459B85-4443-4584-AD2F-9B49E04CBB96}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{42AF3FAB-F203-4132-9DAC-0BF121936304}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -3763,7 +3763,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03D80C54-9B97-43D1-A7DF-B0D00E836335}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87B24CFF-3428-46F9-B45C-D9E70E715F4B}">
   <dimension ref="B3:L489"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BA6B77CE-D63C-4B75-AE47-4F3D78462FF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2709E61D-5CAF-4CF8-919B-0EA553FAB009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{42AF3FAB-F203-4132-9DAC-0BF121936304}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{72DE3796-43AF-4109-8C60-4F1C011877B1}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -3763,7 +3763,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87B24CFF-3428-46F9-B45C-D9E70E715F4B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03A24048-3649-4826-B750-D28A58749617}">
   <dimension ref="B3:L489"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2709E61D-5CAF-4CF8-919B-0EA553FAB009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E993707-BC59-4D2A-A20B-EFE15939E32E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{72DE3796-43AF-4109-8C60-4F1C011877B1}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{BEA24FFF-CF81-4418-BD9E-DB34A88F5AA8}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -3763,7 +3763,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03A24048-3649-4826-B750-D28A58749617}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{495AB70F-8B2C-4BCC-BA67-4D18EE0C1D43}">
   <dimension ref="B3:L489"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E993707-BC59-4D2A-A20B-EFE15939E32E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C0B96DBE-91A3-470E-B6B4-00404A9D7467}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{BEA24FFF-CF81-4418-BD9E-DB34A88F5AA8}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{4248C642-DB8E-4BE4-AF34-D94B763E8EBC}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -3763,7 +3763,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{495AB70F-8B2C-4BCC-BA67-4D18EE0C1D43}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6E75F43-A294-46BC-A145-0F1BB4EF3C8B}">
   <dimension ref="B3:L489"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C0B96DBE-91A3-470E-B6B4-00404A9D7467}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{27B8A90F-FE0B-4507-AA27-BA7EEF618CDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{4248C642-DB8E-4BE4-AF34-D94B763E8EBC}"/>
+    <workbookView xWindow="1103" yWindow="1103" windowWidth="21600" windowHeight="12682" xr2:uid="{C7CA62FA-468F-4EF4-93F7-4FDD87219658}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -3763,7 +3763,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6E75F43-A294-46BC-A145-0F1BB4EF3C8B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{314A6696-378F-4C63-8CE4-D5ABF014D82C}">
   <dimension ref="B3:L489"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{27B8A90F-FE0B-4507-AA27-BA7EEF618CDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8DBB0489-00A3-4203-83C4-15D4DF534768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1103" yWindow="1103" windowWidth="21600" windowHeight="12682" xr2:uid="{C7CA62FA-468F-4EF4-93F7-4FDD87219658}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="21600" windowHeight="12683" xr2:uid="{D2E60EEB-E53E-42D6-A57B-09FC40FE7839}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -3763,7 +3763,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{314A6696-378F-4C63-8CE4-D5ABF014D82C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F7B46B4-D124-4E3B-A8AD-A1A6F19E7CC6}">
   <dimension ref="B3:L489"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8DBB0489-00A3-4203-83C4-15D4DF534768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8CCA0C44-E376-4A4B-8F72-D7C801599DC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="21600" windowHeight="12683" xr2:uid="{D2E60EEB-E53E-42D6-A57B-09FC40FE7839}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{93D87073-2383-4CEB-AE32-1339E2C03679}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -3763,7 +3763,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F7B46B4-D124-4E3B-A8AD-A1A6F19E7CC6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7D40331-2045-4B5E-B9A0-4B9C36C8CB6E}">
   <dimension ref="B3:L489"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8CCA0C44-E376-4A4B-8F72-D7C801599DC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{97670242-97EC-4E25-A56A-7E7B9F21D795}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{93D87073-2383-4CEB-AE32-1339E2C03679}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{D0910A7D-AE40-4D01-A05D-B825C42786B4}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -3763,7 +3763,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7D40331-2045-4B5E-B9A0-4B9C36C8CB6E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F02641-336D-4B8C-81E9-A90630167819}">
   <dimension ref="B3:L489"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{97670242-97EC-4E25-A56A-7E7B9F21D795}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4EFA5189-CAF8-4C5D-A505-70A9A0817253}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{D0910A7D-AE40-4D01-A05D-B825C42786B4}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{7064F54A-1DC8-46BE-A94B-6B4E3D573E85}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -3763,7 +3763,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F02641-336D-4B8C-81E9-A90630167819}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28C3F2AF-9758-487F-B3E5-39A8FE86A188}">
   <dimension ref="B3:L489"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4EFA5189-CAF8-4C5D-A505-70A9A0817253}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B2375A94-6D30-413A-904D-D069C325DE4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{7064F54A-1DC8-46BE-A94B-6B4E3D573E85}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{B08DBE85-5DF6-43E4-93B9-DE9EF7EF4FC3}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -3763,7 +3763,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28C3F2AF-9758-487F-B3E5-39A8FE86A188}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7444B25D-7672-4C9E-9A92-2C74EE625783}">
   <dimension ref="B3:L489"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B2375A94-6D30-413A-904D-D069C325DE4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0498C7C6-1767-4C7A-91E5-B0C811BAB256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{B08DBE85-5DF6-43E4-93B9-DE9EF7EF4FC3}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{9FA28256-8E0B-46DB-868C-8B93D0D4BDF8}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -3763,7 +3763,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7444B25D-7672-4C9E-9A92-2C74EE625783}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E519F4AD-15E7-46EE-A2E6-2C688EDBC059}">
   <dimension ref="B3:L489"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0498C7C6-1767-4C7A-91E5-B0C811BAB256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{80A70573-1D78-4B92-8C63-FBEE3C73D885}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{9FA28256-8E0B-46DB-868C-8B93D0D4BDF8}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{24C251F0-AD19-4DFA-B51F-468376EC14AD}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -3763,7 +3763,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E519F4AD-15E7-46EE-A2E6-2C688EDBC059}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8A3A0C2-283E-46E6-ACD0-ACF6C21C6527}">
   <dimension ref="B3:L489"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{80A70573-1D78-4B92-8C63-FBEE3C73D885}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{800F19F7-F9B9-4CB7-B8B4-6EC29474E2C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{24C251F0-AD19-4DFA-B51F-468376EC14AD}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{9D5EC2F3-7C9C-49AD-9CC0-A9806771E55D}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -3763,7 +3763,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8A3A0C2-283E-46E6-ACD0-ACF6C21C6527}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E97F4E4-1B93-4555-A3F1-BE4DD8BB0AC5}">
   <dimension ref="B3:L489"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{800F19F7-F9B9-4CB7-B8B4-6EC29474E2C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4D625C58-C9AB-4100-B0B6-4E7A799EBC57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{9D5EC2F3-7C9C-49AD-9CC0-A9806771E55D}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{D3C5650C-1749-48F7-889B-EA111CF6294F}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -3763,7 +3763,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E97F4E4-1B93-4555-A3F1-BE4DD8BB0AC5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84B0ED55-8613-4E34-B3FD-444B34FAAFE6}">
   <dimension ref="B3:L489"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4D625C58-C9AB-4100-B0B6-4E7A799EBC57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1BCBA233-3C4C-4A34-B548-98CDB475D3F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{D3C5650C-1749-48F7-889B-EA111CF6294F}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{905A9C28-612B-40D8-B900-26A52288E9CD}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -3763,7 +3763,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84B0ED55-8613-4E34-B3FD-444B34FAAFE6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C262C5F-02A9-4D0C-88EC-6CEEBEDF3C11}">
   <dimension ref="B3:L489"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1BCBA233-3C4C-4A34-B548-98CDB475D3F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{750EF355-3C20-4C8F-A559-348E91E296D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{905A9C28-612B-40D8-B900-26A52288E9CD}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{8C1AB5B6-6F68-4538-B13D-9CBCFB8D6E2E}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -3763,7 +3763,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C262C5F-02A9-4D0C-88EC-6CEEBEDF3C11}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56396F1F-25BF-4EDF-ABF9-734081E21486}">
   <dimension ref="B3:L489"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{750EF355-3C20-4C8F-A559-348E91E296D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E5336F0E-BC14-4CD9-A9AD-3A37732CAAB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{8C1AB5B6-6F68-4538-B13D-9CBCFB8D6E2E}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{CB78D576-C4E8-495B-B974-CDC3298A3DC8}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -3763,7 +3763,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56396F1F-25BF-4EDF-ABF9-734081E21486}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB29CC09-C922-4AE7-8043-323C35E4394C}">
   <dimension ref="B3:L489"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E5336F0E-BC14-4CD9-A9AD-3A37732CAAB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{783B1C1A-C352-44F2-BAF2-D55D5037F424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{CB78D576-C4E8-495B-B974-CDC3298A3DC8}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{6F2948CC-8E1A-4692-9A04-47F87B34DD49}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -3763,7 +3763,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB29CC09-C922-4AE7-8043-323C35E4394C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{041F04FA-4EE7-47CF-A41F-2EBC2D9EFA85}">
   <dimension ref="B3:L489"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{783B1C1A-C352-44F2-BAF2-D55D5037F424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B1864C2C-354F-430E-8884-37A81396F2CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{6F2948CC-8E1A-4692-9A04-47F87B34DD49}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{BA255D10-1570-4A34-A3D8-F89B28C939D4}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -3763,7 +3763,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{041F04FA-4EE7-47CF-A41F-2EBC2D9EFA85}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CF29B0B-E1D4-4CA1-A4DD-C8F945334DC9}">
   <dimension ref="B3:L489"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B1864C2C-354F-430E-8884-37A81396F2CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FBF276A1-FADF-4F21-BC27-C07C4D299DDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{BA255D10-1570-4A34-A3D8-F89B28C939D4}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{5C462ED5-E35B-4CFC-8A53-F77A0D3E44FC}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -3763,7 +3763,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CF29B0B-E1D4-4CA1-A4DD-C8F945334DC9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{564F7C44-CDAC-40D7-BC10-1F82F7E4C51D}">
   <dimension ref="B3:L489"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FBF276A1-FADF-4F21-BC27-C07C4D299DDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AED6D572-97D0-478D-96A1-44F5469A11C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{5C462ED5-E35B-4CFC-8A53-F77A0D3E44FC}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{7B7F82AA-045F-4333-8EDA-217AE053A524}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -3763,7 +3763,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{564F7C44-CDAC-40D7-BC10-1F82F7E4C51D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{435BA149-E50D-4B0F-BBD8-12CEE21715D3}">
   <dimension ref="B3:L489"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AED6D572-97D0-478D-96A1-44F5469A11C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D6D89F68-F18F-40AC-99A8-7B68B2118F39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{7B7F82AA-045F-4333-8EDA-217AE053A524}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{3E93202F-E86C-4CFD-A9CB-D01808B36E11}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -3763,7 +3763,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{435BA149-E50D-4B0F-BBD8-12CEE21715D3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B3B3FD5-4B33-479D-82E1-DACFE1799F23}">
   <dimension ref="B3:L489"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D6D89F68-F18F-40AC-99A8-7B68B2118F39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F8649D12-9A13-41A0-9196-3DA7C667F0A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{3E93202F-E86C-4CFD-A9CB-D01808B36E11}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{7EF95C65-DA79-442A-9794-99FA45C374FD}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -3763,7 +3763,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B3B3FD5-4B33-479D-82E1-DACFE1799F23}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0A7018C-1219-4EFC-9241-313CC781E19C}">
   <dimension ref="B3:L489"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F8649D12-9A13-41A0-9196-3DA7C667F0A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{899836DE-06B7-468C-B1C2-43F90E57D231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{7EF95C65-DA79-442A-9794-99FA45C374FD}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{FDB1FC7A-F022-4189-B951-865780528971}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -3763,7 +3763,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0A7018C-1219-4EFC-9241-313CC781E19C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE6C6745-2A57-4B59-A8BA-0A8FDFC2CB3C}">
   <dimension ref="B3:L489"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{899836DE-06B7-468C-B1C2-43F90E57D231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3997F9D4-9DE7-4778-8DB9-CF3796204B92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{FDB1FC7A-F022-4189-B951-865780528971}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{0DD94D44-64FF-4B2D-89B3-572C7BD4C649}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -3763,7 +3763,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE6C6745-2A57-4B59-A8BA-0A8FDFC2CB3C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCBBE5DF-C709-48DE-91C1-414988B5FF0B}">
   <dimension ref="B3:L489"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3997F9D4-9DE7-4778-8DB9-CF3796204B92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5588F3E8-5945-4B80-AB44-F41813688216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{0DD94D44-64FF-4B2D-89B3-572C7BD4C649}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{F71502F8-575F-4D71-B047-68870960B2C8}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -3763,7 +3763,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCBBE5DF-C709-48DE-91C1-414988B5FF0B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BD5C37D-0F02-4BE2-B1B1-1871F2192A0D}">
   <dimension ref="B3:L489"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5588F3E8-5945-4B80-AB44-F41813688216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CE9304AC-32C4-4931-B5F6-09F95F742A76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{F71502F8-575F-4D71-B047-68870960B2C8}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{F0DC471C-E203-42DE-9A9B-50A4369D2388}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -3763,7 +3763,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BD5C37D-0F02-4BE2-B1B1-1871F2192A0D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B29F4AB-EB65-4AEB-9C11-45C75C28787F}">
   <dimension ref="B3:L489"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CE9304AC-32C4-4931-B5F6-09F95F742A76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A621EEDF-7754-44F7-98F8-DD908B663E13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{F0DC471C-E203-42DE-9A9B-50A4369D2388}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{58DB8603-EF86-454F-BCD1-FF833B67F798}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -3763,7 +3763,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B29F4AB-EB65-4AEB-9C11-45C75C28787F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD35909C-E248-4486-94F1-551EDED2B219}">
   <dimension ref="B3:L489"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A621EEDF-7754-44F7-98F8-DD908B663E13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A64EDCF3-9A11-4E46-8F4F-8A474F9D011B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{58DB8603-EF86-454F-BCD1-FF833B67F798}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{365E5ED9-76D7-4A0B-AAC3-8556692C2747}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -3763,7 +3763,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD35909C-E248-4486-94F1-551EDED2B219}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62EA907B-F50E-4B88-86D6-EBA64FD9BD24}">
   <dimension ref="B3:L489"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A64EDCF3-9A11-4E46-8F4F-8A474F9D011B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{375ADFDF-7AF1-4A2D-B5C8-F8C1A24BACE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{365E5ED9-76D7-4A0B-AAC3-8556692C2747}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{89F9F65D-7D8B-49B0-84F1-60283EF8223B}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -3763,7 +3763,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62EA907B-F50E-4B88-86D6-EBA64FD9BD24}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F9E8865-2261-4372-83B6-35FAFF5EB14B}">
   <dimension ref="B3:L489"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
